--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masahiro inui\Desktop\my-history-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F70F972-7ACE-49E9-A907-B1688C31335E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC95B7C-4657-4E53-A2BF-5E1FDC0A13CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{61091AB9-7A2E-4462-BF1F-C6BF033D5550}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{61091AB9-7A2E-4462-BF1F-C6BF033D5550}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>世界最古の人類を何というか。カタカナで答えなさい。</t>
     <rPh sb="0" eb="4">
@@ -76,6 +76,877 @@
     <rPh sb="0" eb="2">
       <t>エンジン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人類とその他の動物との違いとして後ろ足２本で立って歩けることを何というか。</t>
+    <rPh sb="0" eb="2">
+      <t>ジンルイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ドウブツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ウシ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アシ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>直立二足歩行</t>
+    <rPh sb="0" eb="6">
+      <t>チョクリツニソクホコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>猿人から進化を遂げて、火や言葉を使えるようになった人類を何というか。</t>
+    <rPh sb="0" eb="2">
+      <t>エンジン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シンカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジンルイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原人</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>猿人との違いとして原人が使えるようになったものは言葉と何か。</t>
+    <rPh sb="0" eb="2">
+      <t>エンジン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゲンジン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言葉</t>
+    <rPh sb="0" eb="2">
+      <t>コトバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>猿人との違いとして原人が使えるようになったものは火と何か。</t>
+    <rPh sb="0" eb="2">
+      <t>エンジン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゲンジン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原人や猿人が用いたと考えられる、石を打ち割って作る道具を何というか。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エンジン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ドウグ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打製石器</t>
+    <rPh sb="0" eb="4">
+      <t>ダセイセッキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>旧石器時代</t>
+    <rPh sb="0" eb="5">
+      <t>キュウセッキジダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打製石器を使って狩猟採集生活を送っていた時代を何というか。</t>
+    <rPh sb="0" eb="4">
+      <t>ダセイセッキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイカツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジダイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在の人類の直接の祖先と考えらる人種を何というか、漢字で答えなさい。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジンルイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ソセン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジンシュ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在の人類の直接の祖先と考えらる人種を何というか、カタカナで答えなさい。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジンルイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ソセン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジンシュ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新人</t>
+    <rPh sb="0" eb="2">
+      <t>シンジン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホモサピエンス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古代の人々が、自分たちの子孫に残したと考えられる洞窟壁画が残されているフランスの町はどこか。</t>
+    <rPh sb="0" eb="2">
+      <t>コダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒトビト</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シソン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ドウクツ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヘキガ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラスコー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷期が終わり、狩猟採集生活から農耕牧畜生活へと変化した時代を何というか。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="7" eb="13">
+      <t>シュリョウサイシュウセイカツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ノウコウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ボクチク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイカツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ジダイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新石器時代</t>
+    <rPh sb="0" eb="5">
+      <t>シンセッキジダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>磨製石器</t>
+    <rPh sb="0" eb="4">
+      <t>マセイセッキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新石器時代に使われていた、石をみがいて作る道具を何というか。</t>
+    <rPh sb="0" eb="3">
+      <t>シンセッキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジダイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ドウグ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新石器時代に入り、生産した作物を貯蔵したり煮炊きするために用いた道具とは何か。</t>
+    <rPh sb="0" eb="5">
+      <t>シンセッキジダイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チョゾウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニタ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ドウグ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>土器</t>
+    <rPh sb="0" eb="2">
+      <t>ドキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４大文明の共通点は、文字と何があることか答えなさい。</t>
+    <rPh sb="1" eb="4">
+      <t>ダイブンメイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>キョウツウテン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４大文明の共通点は、金属器と何があることか答えなさい。</t>
+    <rPh sb="1" eb="4">
+      <t>ダイブンメイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>キョウツウテン</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>キンゾクキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金属器</t>
+    <rPh sb="0" eb="3">
+      <t>キンゾクキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古代文明で主に用いられた銅と錫の混合物で作られた金属を何というか。</t>
+    <rPh sb="0" eb="4">
+      <t>コダイブンメイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スズ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>コンゴウブツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>キンゾク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青銅</t>
+    <rPh sb="0" eb="2">
+      <t>セイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メソポタミア文明が誕生したのはチグリス川と何川の間か。</t>
+    <rPh sb="6" eb="8">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タンジョウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナニガワ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アイダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メソポタミア文明が誕生したのはユーフラテス川と何川の間か。</t>
+    <rPh sb="6" eb="8">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タンジョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ナニガワ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アイダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーフラテス川</t>
+    <rPh sb="6" eb="7">
+      <t>ガワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チグリス川</t>
+    <rPh sb="4" eb="5">
+      <t>ガワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チグリス川とユーフラテス川の間で誕生した文明と名何か。</t>
+    <rPh sb="4" eb="5">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>タンジョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ナナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メソポタミア文明</t>
+    <rPh sb="6" eb="8">
+      <t>ブンメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メソポタミア文明で用いられた文字とは何か。</t>
+    <rPh sb="6" eb="8">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くさび形文字</t>
+    <rPh sb="3" eb="6">
+      <t>ガタモジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メソポタミア文明で用いられた暦を何というか。</t>
+    <rPh sb="6" eb="8">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>コヨミ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>太陰暦</t>
+    <rPh sb="0" eb="3">
+      <t>タイインレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メソポタミア文明で用いられた数の数え方を何というか。</t>
+    <rPh sb="6" eb="8">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カゾ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>６０進法</t>
+    <rPh sb="2" eb="4">
+      <t>シンホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メソポタミア文明で作られた「目には目をなどの決まりを持つ法を何というか。</t>
+    <rPh sb="6" eb="8">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハンムラビ法典</t>
+    <rPh sb="5" eb="7">
+      <t>ホウテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紀元前３０００年ごろにナイル川流域に誕生した文明とは何か。</t>
+    <rPh sb="0" eb="3">
+      <t>キゲンゼン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ガワリュウイキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>タンジョウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エジプト文明</t>
+    <rPh sb="4" eb="6">
+      <t>ブンメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ナイル川</t>
+    <rPh sb="3" eb="4">
+      <t>ガワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エジプト文明が誕生したのは何川流域か。</t>
+    <rPh sb="4" eb="6">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>タンジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ナニガワ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>リュウイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古代エジプトでは王の事を何と呼んだか。</t>
+    <rPh sb="0" eb="2">
+      <t>コダイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファラオ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古代エジプトの王たちの墓と考えられているものは何か。</t>
+    <rPh sb="0" eb="2">
+      <t>コダイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピラミッド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エジプト文明で用いられた文字を何というか。</t>
+    <rPh sb="4" eb="6">
+      <t>ブンメイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>象形文字</t>
+    <rPh sb="0" eb="4">
+      <t>ショウケイモジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>太陽暦</t>
+    <rPh sb="0" eb="3">
+      <t>タイヨウレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古代エジプトで用いられた暦を何というか。</t>
+    <rPh sb="0" eb="2">
+      <t>コダイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>コヨミ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古代エジプトで紙の代わりになっていたものを何というか。</t>
+    <rPh sb="0" eb="2">
+      <t>コダイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パピルス</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -441,8 +1312,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{096C5398-236E-4954-9C39-C749D2DB51E6}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="71.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -458,6 +1333,238 @@
       </c>
       <c r="B2" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
